--- a/testdata/Data.xlsx
+++ b/testdata/Data.xlsx
@@ -1,40 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\myworkspace\Opencart_V122_Cucumber\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Samad\Selenium\Outside projects\Opencart_V122_Cucumber\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DD2E2C-A9D7-446F-BE12-6472CD00CF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F925E0-4A72-4798-901B-842376C72799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Valid</t>
   </si>
@@ -42,9 +33,6 @@
     <t>Invalid</t>
   </si>
   <si>
-    <t>pavanoltraining@gmail.com</t>
-  </si>
-  <si>
     <t>test@123</t>
   </si>
   <si>
@@ -70,6 +58,12 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t>samadraza90@gmail.com</t>
+  </si>
+  <si>
+    <t>test@12345</t>
   </si>
 </sst>
 </file>
@@ -192,9 +186,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +226,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +332,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +474,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,82 +483,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884FCF78-0A3E-40BF-9E26-11C478AF56E2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="34.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2"/>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
@@ -572,17 +566,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{D3BE7519-95C3-4ACD-9AB4-5385C9508082}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
-    <hyperlink ref="B2" r:id="rId4" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{B4FF4FF2-C3C7-488B-A3F2-29DB9D3EA93F}"/>
-    <hyperlink ref="B4" r:id="rId8" xr:uid="{8805FB17-496E-4860-A407-7E85792F066A}"/>
-    <hyperlink ref="A5" r:id="rId9" xr:uid="{B32BC020-9B23-4A13-8CF8-3C376BFFBFA3}"/>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
+    <hyperlink ref="A6" r:id="rId3" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{B4FF4FF2-C3C7-488B-A3F2-29DB9D3EA93F}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{8805FB17-496E-4860-A407-7E85792F066A}"/>
+    <hyperlink ref="A5" r:id="rId7" xr:uid="{B32BC020-9B23-4A13-8CF8-3C376BFFBFA3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId10"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e760c494-6550-44b4-8258-77c175d778b7}" enabled="1" method="Privileged" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>